--- a/data/trans_orig/P04C05_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>186039</t>
+          <t>185416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239330</t>
+          <t>238710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159682</t>
+          <t>161427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>232733</t>
+          <t>229703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>368515</t>
+          <t>364967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455677</t>
+          <t>453321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>391560</t>
+          <t>391655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>446315</t>
+          <t>445673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>487083</t>
+          <t>490358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>561898</t>
+          <t>558716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>894532</t>
+          <t>897917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>983521</t>
+          <t>990363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96745</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230104</t>
+          <t>227963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>185807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234726</t>
+          <t>233444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258398</t>
+          <t>255021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442476</t>
+          <t>446120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27524</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>949729</t>
+          <t>952802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1089723</t>
+          <t>1103774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>712599</t>
+          <t>713141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>759169</t>
+          <t>761109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1686310</t>
+          <t>1682254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1881915</t>
+          <t>1881524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>198965</t>
+          <t>196668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255113</t>
+          <t>255815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137931</t>
+          <t>125922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>342359</t>
+          <t>345611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>314846</t>
+          <t>328351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>564326</t>
+          <t>570118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>438900</t>
+          <t>437161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496168</t>
+          <t>496798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>584604</t>
+          <t>582353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>792282</t>
+          <t>804469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1055644</t>
+          <t>1050530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1314991</t>
+          <t>1300781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147449</t>
+          <t>144275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195638</t>
+          <t>194786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229962</t>
+          <t>230026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>437537</t>
+          <t>454689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392401</t>
+          <t>393527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>658857</t>
+          <t>659239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44549</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>713651</t>
+          <t>713758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>764300</t>
+          <t>765608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>644345</t>
+          <t>618202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>847767</t>
+          <t>845887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1334895</t>
+          <t>1331531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1596430</t>
+          <t>1594076</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>617313</t>
+          <t>587270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>857821</t>
+          <t>860060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>810917</t>
+          <t>821691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1115023</t>
+          <t>1121098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1517268</t>
+          <t>1517165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1917868</t>
+          <t>1916964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56234</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41465</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58432</t>
+          <t>57314</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>90684</t>
+          <t>91208</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2555774</t>
+          <t>2552235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2806529</t>
+          <t>2841414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2562267</t>
+          <t>2554007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2873706</t>
+          <t>2859473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5180703</t>
+          <t>5168614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5593033</t>
+          <t>5576810</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C05_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>209940</t>
+          <t>238408</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>185416</t>
+          <t>212739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238710</t>
+          <t>266843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>206239</t>
+          <t>226014</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161427</t>
+          <t>205581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229703</t>
+          <t>248170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>416179</t>
+          <t>464423</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>364967</t>
+          <t>428590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>453321</t>
+          <t>500570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>420390</t>
+          <t>446921</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>391655</t>
+          <t>418032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>445673</t>
+          <t>473143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>514022</t>
+          <t>502888</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>490358</t>
+          <t>480287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>558716</t>
+          <t>522713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>934411</t>
+          <t>949810</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>897917</t>
+          <t>911930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>990363</t>
+          <t>984959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>724207</t>
+          <t>733109</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724207</t>
+          <t>733109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>724207</t>
+          <t>733109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1358628</t>
+          <t>1422733</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1358628</t>
+          <t>1422733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1358628</t>
+          <t>1422733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>212343</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84268</t>
+          <t>185475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227963</t>
+          <t>242696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>209899</t>
+          <t>238905</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185807</t>
+          <t>212623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233444</t>
+          <t>265088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>383577</t>
+          <t>451248</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>255021</t>
+          <t>410578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446120</t>
+          <t>490819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14901</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28614</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1009690</t>
+          <t>822559</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>952802</t>
+          <t>791168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1103774</t>
+          <t>848691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>737386</t>
+          <t>818636</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>713141</t>
+          <t>790885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>761109</t>
+          <t>844003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1747076</t>
+          <t>1641195</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1682254</t>
+          <t>1601415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1881524</t>
+          <t>1682071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>956265</t>
+          <t>1067987</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>956265</t>
+          <t>1067987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>956265</t>
+          <t>1067987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149129</t>
+          <t>2116904</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149129</t>
+          <t>2116904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149129</t>
+          <t>2116904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>225730</t>
+          <t>266720</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196668</t>
+          <t>237736</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255815</t>
+          <t>298882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257911</t>
+          <t>305999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125922</t>
+          <t>278686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345611</t>
+          <t>329938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>483641</t>
+          <t>572719</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>328351</t>
+          <t>529730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>570118</t>
+          <t>613491</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>468177</t>
+          <t>521321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>437161</t>
+          <t>488594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496798</t>
+          <t>551792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>670830</t>
+          <t>496618</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582353</t>
+          <t>470126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>804469</t>
+          <t>524030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1139006</t>
+          <t>1017939</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1050530</t>
+          <t>976942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1300781</t>
+          <t>1059269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932078</t>
+          <t>810871</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932078</t>
+          <t>810871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932078</t>
+          <t>810871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1636593</t>
+          <t>1612766</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1636593</t>
+          <t>1612766</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1636593</t>
+          <t>1612766</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>170040</t>
+          <t>187695</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144275</t>
+          <t>161484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194786</t>
+          <t>213992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>291615</t>
+          <t>245426</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>230026</t>
+          <t>221202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>454689</t>
+          <t>271656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>461655</t>
+          <t>433121</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>393527</t>
+          <t>398994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>659239</t>
+          <t>471511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>33369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22564</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>739628</t>
+          <t>780056</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>713758</t>
+          <t>752959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>765608</t>
+          <t>804747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>786918</t>
+          <t>854885</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>618202</t>
+          <t>825369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>845887</t>
+          <t>877173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1526547</t>
+          <t>1634942</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1331531</t>
+          <t>1594943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1594076</t>
+          <t>1669692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925857</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925857</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925857</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2020060</t>
+          <t>2107415</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2020060</t>
+          <t>2107415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2020060</t>
+          <t>2107415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>779388</t>
+          <t>905166</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>587270</t>
+          <t>846007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>860060</t>
+          <t>964055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>965663</t>
+          <t>1016345</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>821691</t>
+          <t>965689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1121098</t>
+          <t>1061901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1745051</t>
+          <t>1921511</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1517165</t>
+          <t>1850449</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1916964</t>
+          <t>2001015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>94422</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57314</t>
+          <t>77379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91208</t>
+          <t>116483</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2637885</t>
+          <t>2570857</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2552235</t>
+          <t>2511714</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2841414</t>
+          <t>2629919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2709156</t>
+          <t>2673028</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2554007</t>
+          <t>2624425</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2859473</t>
+          <t>2724674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5347041</t>
+          <t>5243886</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5168614</t>
+          <t>5162112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5576810</t>
+          <t>5316237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
